--- a/香港現在上映電影 2025-07-28.xlsx
+++ b/香港現在上映電影 2025-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="166">
   <si>
     <t>英文名稱</t>
   </si>
@@ -70,6 +70,9 @@
     <t>夢遊納米比亞沙漠</t>
   </si>
   <si>
+    <t>逃婚緣記</t>
+  </si>
+  <si>
     <t>小婦人尋夫記</t>
   </si>
   <si>
@@ -94,21 +97,12 @@
     <t>腓尼基大作戰</t>
   </si>
   <si>
-    <t>殺神John Wick之芭蕾殺姬</t>
-  </si>
-  <si>
     <t>馴龍記</t>
   </si>
   <si>
     <t>史迪仔</t>
   </si>
   <si>
-    <t>直男脫單大作戰</t>
-  </si>
-  <si>
-    <t>F9 狂野時速</t>
-  </si>
-  <si>
     <t>人工殺姬 2.0</t>
   </si>
   <si>
@@ -148,6 +142,9 @@
     <t>Desert of Namibia</t>
   </si>
   <si>
+    <t>Grand Tour</t>
+  </si>
+  <si>
     <t>Shambhala</t>
   </si>
   <si>
@@ -172,21 +169,12 @@
     <t>The Phoenician Scheme</t>
   </si>
   <si>
-    <t>From the World of John Wick: Ballerina</t>
-  </si>
-  <si>
     <t>How to Train Your Dragon</t>
   </si>
   <si>
     <t>Lilo &amp; Stitch</t>
   </si>
   <si>
-    <t>The Dating Game</t>
-  </si>
-  <si>
-    <t>Fast &amp; Furious 9</t>
-  </si>
-  <si>
     <t>M3GAN 2.0</t>
   </si>
   <si>
@@ -226,6 +214,9 @@
     <t>6/9/2024</t>
   </si>
   <si>
+    <t>26/9/2024</t>
+  </si>
+  <si>
     <t>8/11/2024</t>
   </si>
   <si>
@@ -250,12 +241,6 @@
     <t>10/5/2025</t>
   </si>
   <si>
-    <t>23/1/2025</t>
-  </si>
-  <si>
-    <t>19/5/2021</t>
-  </si>
-  <si>
     <t>26/6/2025</t>
   </si>
   <si>
@@ -310,18 +295,12 @@
     <t>喜劇、動作、犯罪</t>
   </si>
   <si>
-    <t>動作、驚悚</t>
-  </si>
-  <si>
     <t>親子、奇幻、冒險、動作、喜劇</t>
   </si>
   <si>
     <t>親子、喜劇、科幻、動作、冒險</t>
   </si>
   <si>
-    <t>動作、冒險、犯罪</t>
-  </si>
-  <si>
     <t>科幻、動作、恐怖、喜劇</t>
   </si>
   <si>
@@ -352,15 +331,15 @@
     <t>1h 32m</t>
   </si>
   <si>
+    <t>2h 9m</t>
+  </si>
+  <si>
     <t>2h 30m</t>
   </si>
   <si>
     <t>1h 55m</t>
   </si>
   <si>
-    <t>2h 9m</t>
-  </si>
-  <si>
     <t>2h 35m</t>
   </si>
   <si>
@@ -379,12 +358,6 @@
     <t>1h 48m</t>
   </si>
   <si>
-    <t>1h 30m</t>
-  </si>
-  <si>
-    <t>2h 25m</t>
-  </si>
-  <si>
     <t>2h 0m</t>
   </si>
   <si>
@@ -409,46 +382,46 @@
     <t>III</t>
   </si>
   <si>
-    <t>TBC</t>
-  </si>
-  <si>
     <t>27.38萬</t>
   </si>
   <si>
-    <t>39.81億</t>
-  </si>
-  <si>
-    <t>28.72億</t>
-  </si>
-  <si>
-    <t>2.834億</t>
-  </si>
-  <si>
-    <t>5495萬</t>
-  </si>
-  <si>
-    <t>22.40億</t>
+    <t>39.80億</t>
+  </si>
+  <si>
+    <t>28.71億</t>
+  </si>
+  <si>
+    <t>2.833億</t>
+  </si>
+  <si>
+    <t>5494萬</t>
+  </si>
+  <si>
+    <t>22.39億</t>
   </si>
   <si>
     <t>30.19萬</t>
   </si>
   <si>
+    <t>622.7萬</t>
+  </si>
+  <si>
     <t>6444</t>
   </si>
   <si>
-    <t>11.78億</t>
-  </si>
-  <si>
-    <t>17.11億</t>
-  </si>
-  <si>
-    <t>39.46億</t>
-  </si>
-  <si>
-    <t>40.01億</t>
-  </si>
-  <si>
-    <t>10.40億</t>
+    <t>11.77億</t>
+  </si>
+  <si>
+    <t>17.01億</t>
+  </si>
+  <si>
+    <t>39.53億</t>
+  </si>
+  <si>
+    <t>40.10億</t>
+  </si>
+  <si>
+    <t>10.84億</t>
   </si>
   <si>
     <t>46.47億</t>
@@ -457,31 +430,25 @@
     <t>3.011億</t>
   </si>
   <si>
-    <t>10.35億</t>
-  </si>
-  <si>
-    <t>47.56億</t>
-  </si>
-  <si>
-    <t>79.30億</t>
-  </si>
-  <si>
-    <t>57億</t>
+    <t>47.60億</t>
+  </si>
+  <si>
+    <t>79.95億</t>
   </si>
   <si>
     <t>3.043億</t>
   </si>
   <si>
-    <t>56.39億</t>
+    <t>56.50億</t>
   </si>
   <si>
     <t>7962萬</t>
   </si>
   <si>
-    <t>3.576億</t>
-  </si>
-  <si>
-    <t>5.423億</t>
+    <t>3.584億</t>
+  </si>
+  <si>
+    <t>5.427億</t>
   </si>
   <si>
     <t>100</t>
@@ -502,6 +469,9 @@
     <t>92</t>
   </si>
   <si>
+    <t>90</t>
+  </si>
+  <si>
     <t>89</t>
   </si>
   <si>
@@ -527,12 +497,6 @@
   </si>
   <si>
     <t>72</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>59</t>
   </si>
   <si>
     <t>57</t>
@@ -943,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="1" customWidth="1"/>
@@ -996,25 +960,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G2" s="1">
         <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1022,19 +986,19 @@
         <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G3" s="1">
         <v>70</v>
@@ -1046,10 +1010,10 @@
         <v>50</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1057,19 +1021,19 @@
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1">
         <v>49</v>
@@ -1081,10 +1045,10 @@
         <v>10000</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1092,19 +1056,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G5" s="1">
         <v>402</v>
@@ -1116,10 +1080,10 @@
         <v>25000</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1127,19 +1091,19 @@
         <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G6" s="1">
         <v>197</v>
@@ -1151,10 +1115,10 @@
         <v>500</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1162,19 +1126,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G7" s="1">
         <v>37</v>
@@ -1183,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1194,19 +1158,19 @@
         <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G8" s="1">
         <v>223</v>
@@ -1218,10 +1182,10 @@
         <v>5000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1229,28 +1193,28 @@
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="G9" s="1">
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1258,31 +1222,31 @@
         <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="G10" s="1">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1290,34 +1254,31 @@
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G11" s="1">
-        <v>365</v>
-      </c>
-      <c r="H11" s="1">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1325,34 +1286,34 @@
         <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G12" s="1">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="H12" s="1">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="I12" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1360,34 +1321,34 @@
         <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="1">
+        <v>321</v>
+      </c>
+      <c r="H13" s="1">
         <v>93</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" s="1">
-        <v>458</v>
-      </c>
-      <c r="H13" s="1">
-        <v>91</v>
-      </c>
       <c r="I13" s="1">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1395,34 +1356,34 @@
         <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G14" s="1">
-        <v>339</v>
+        <v>459</v>
       </c>
       <c r="H14" s="1">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I14" s="1">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1430,34 +1391,34 @@
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G15" s="1">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="H15" s="1">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I15" s="1">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1465,34 +1426,34 @@
         <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="G16" s="1">
-        <v>413</v>
+        <v>217</v>
       </c>
       <c r="H16" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I16" s="1">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1500,34 +1461,34 @@
         <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G17" s="1">
+        <v>413</v>
+      </c>
+      <c r="H17" s="1">
+        <v>88</v>
+      </c>
+      <c r="I17" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G17" s="1">
-        <v>277</v>
-      </c>
-      <c r="H17" s="1">
-        <v>70</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="K17" s="4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1535,34 +1496,34 @@
         <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G18" s="1">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H18" s="1">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I18" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1570,19 +1531,19 @@
         <v>27</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G19" s="1">
         <v>246</v>
@@ -1594,10 +1555,10 @@
         <v>10000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1605,19 +1566,19 @@
         <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G20" s="1">
         <v>211</v>
@@ -1629,10 +1590,10 @@
         <v>10000</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1640,25 +1601,34 @@
         <v>29</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G21" s="1">
-        <v>18</v>
+        <v>228</v>
+      </c>
+      <c r="H21" s="1">
+        <v>82</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1000</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1666,34 +1636,34 @@
         <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G22" s="1">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="H22" s="1">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I22" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1701,34 +1671,34 @@
         <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="G23" s="1">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="H23" s="1">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I23" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1736,34 +1706,34 @@
         <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G24" s="1">
-        <v>368</v>
+        <v>182</v>
       </c>
       <c r="H24" s="1">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I24" s="1">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1771,104 +1741,34 @@
         <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G25" s="1">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H25" s="1">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="I25" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G26" s="1">
-        <v>182</v>
-      </c>
-      <c r="H26" s="1">
-        <v>69</v>
-      </c>
-      <c r="I26" s="1">
-        <v>1000</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="1">
-        <v>89</v>
-      </c>
-      <c r="H27" s="1">
-        <v>65</v>
-      </c>
-      <c r="I27" s="1">
-        <v>500</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1923,19 +1823,19 @@
     <hyperlink ref="A14" r:id="rId48"/>
     <hyperlink ref="B14" r:id="rId49"/>
     <hyperlink ref="F14" r:id="rId50"/>
-    <hyperlink ref="K14" r:id="rId51"/>
+    <hyperlink ref="K14" r:id="rId51" location="tab=summary"/>
     <hyperlink ref="A15" r:id="rId52"/>
     <hyperlink ref="B15" r:id="rId53"/>
     <hyperlink ref="F15" r:id="rId54"/>
-    <hyperlink ref="K15" r:id="rId55" location="tab=summary"/>
+    <hyperlink ref="K15" r:id="rId55"/>
     <hyperlink ref="A16" r:id="rId56"/>
     <hyperlink ref="B16" r:id="rId57"/>
     <hyperlink ref="F16" r:id="rId58"/>
-    <hyperlink ref="K16" r:id="rId59"/>
+    <hyperlink ref="K16" r:id="rId59" location="tab=summary"/>
     <hyperlink ref="A17" r:id="rId60"/>
     <hyperlink ref="B17" r:id="rId61"/>
     <hyperlink ref="F17" r:id="rId62"/>
-    <hyperlink ref="K17" r:id="rId63" location="tab=summary"/>
+    <hyperlink ref="K17" r:id="rId63"/>
     <hyperlink ref="A18" r:id="rId64"/>
     <hyperlink ref="B18" r:id="rId65"/>
     <hyperlink ref="F18" r:id="rId66"/>
@@ -1951,30 +1851,23 @@
     <hyperlink ref="A21" r:id="rId76"/>
     <hyperlink ref="B21" r:id="rId77"/>
     <hyperlink ref="F21" r:id="rId78"/>
-    <hyperlink ref="A22" r:id="rId79"/>
-    <hyperlink ref="B22" r:id="rId80"/>
-    <hyperlink ref="F22" r:id="rId81"/>
-    <hyperlink ref="K22" r:id="rId82"/>
-    <hyperlink ref="A23" r:id="rId83"/>
-    <hyperlink ref="B23" r:id="rId84"/>
-    <hyperlink ref="F23" r:id="rId85"/>
-    <hyperlink ref="K23" r:id="rId86" location="tab=summary"/>
-    <hyperlink ref="A24" r:id="rId87"/>
-    <hyperlink ref="B24" r:id="rId88"/>
-    <hyperlink ref="F24" r:id="rId89"/>
-    <hyperlink ref="K24" r:id="rId90" location="tab=summary"/>
-    <hyperlink ref="A25" r:id="rId91"/>
-    <hyperlink ref="B25" r:id="rId92"/>
-    <hyperlink ref="F25" r:id="rId93"/>
-    <hyperlink ref="K25" r:id="rId94" location="tab=summary"/>
-    <hyperlink ref="A26" r:id="rId95"/>
-    <hyperlink ref="B26" r:id="rId96"/>
-    <hyperlink ref="F26" r:id="rId97"/>
-    <hyperlink ref="K26" r:id="rId98" location="tab=summary"/>
-    <hyperlink ref="A27" r:id="rId99"/>
-    <hyperlink ref="B27" r:id="rId100"/>
-    <hyperlink ref="F27" r:id="rId101"/>
-    <hyperlink ref="K27" r:id="rId102" location="tab=summary"/>
+    <hyperlink ref="K21" r:id="rId79" location="tab=summary"/>
+    <hyperlink ref="A22" r:id="rId80"/>
+    <hyperlink ref="B22" r:id="rId81"/>
+    <hyperlink ref="F22" r:id="rId82"/>
+    <hyperlink ref="K22" r:id="rId83" location="tab=summary"/>
+    <hyperlink ref="A23" r:id="rId84"/>
+    <hyperlink ref="B23" r:id="rId85"/>
+    <hyperlink ref="F23" r:id="rId86"/>
+    <hyperlink ref="K23" r:id="rId87" location="tab=summary"/>
+    <hyperlink ref="A24" r:id="rId88"/>
+    <hyperlink ref="B24" r:id="rId89"/>
+    <hyperlink ref="F24" r:id="rId90"/>
+    <hyperlink ref="K24" r:id="rId91" location="tab=summary"/>
+    <hyperlink ref="A25" r:id="rId92"/>
+    <hyperlink ref="B25" r:id="rId93"/>
+    <hyperlink ref="F25" r:id="rId94"/>
+    <hyperlink ref="K25" r:id="rId95" location="tab=summary"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
